--- a/02-Planning-and-Control/Proposal/Planning-Documents/Current/15. Risk Register v3.xlsx
+++ b/02-Planning-and-Control/Proposal/Planning-Documents/Current/15. Risk Register v3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://autuni-my.sharepoint.com/personal/cgr2690_autuni_ac_nz/Documents/Data/COMP702/Linux Networking/02-Planning-and-Control/Proposal/Proposal Feedback Improvements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="541" documentId="11_8CBA91280E61FE779337C2339044397759FB1751" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{716BC03C-A4EC-4C90-AE34-7E4CEEB916D6}"/>
+  <xr:revisionPtr revIDLastSave="542" documentId="11_8CBA91280E61FE779337C2339044397759FB1751" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{085E8E0D-DDC6-4CB9-82A9-494C30EC5C4A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
   <si>
     <t>Risk Register v2.0</t>
   </si>
@@ -429,16 +429,13 @@
   </si>
   <si>
     <t>Configure Chrony NTP server on all four PCs for consistent time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -870,20 +867,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="34.1796875" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" customWidth="1"/>
-    <col min="7" max="7" width="18.54296875" customWidth="1"/>
-    <col min="8" max="8" width="21.7265625" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="21">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -898,7 +895,7 @@
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.6">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -915,7 +912,7 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15.75" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -950,7 +947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="77.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="77.45">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -985,7 +982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="77.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="77.45">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1020,7 +1017,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="77.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="77.45">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1055,7 +1052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="63.75" customHeight="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1090,7 +1087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="122.25" customHeight="1">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1125,7 +1122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="74.25" customHeight="1">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1160,7 +1157,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="108.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="108.6">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1195,7 +1192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="46.5">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -1230,7 +1227,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="124" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="123.95">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -1265,7 +1262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="77.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="77.45">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1300,7 +1297,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="46.5">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1335,7 +1332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="108.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="108.6">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1370,7 +1367,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="62" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="62.1">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1405,7 +1402,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="77.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="77.45">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1440,7 +1437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="93" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="93">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1475,7 +1472,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="108.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="108.6">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1510,7 +1507,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="124" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="123.95">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1545,7 +1542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="93" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="93">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -1580,7 +1577,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="12" customFormat="1" ht="108.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="12" customFormat="1" ht="108.6">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -1615,7 +1612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="62" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="58.5">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -1647,10 +1644,10 @@
         <v>14</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.6">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1663,7 +1660,7 @@
       <c r="J24" s="11"/>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="15.6">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1676,7 +1673,7 @@
       <c r="J25" s="11"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="15.6">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1689,7 +1686,7 @@
       <c r="J26" s="11"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="15.6">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1702,7 +1699,7 @@
       <c r="J27" s="11"/>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" ht="15.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="15.6">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1729,7 +1726,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.6"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1740,7 +1737,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.6"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
